--- a/AAII_Financials/Quarterly/VLTO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VLTO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>VLTO</t>
   </si>
@@ -656,274 +656,286 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
         <v>46115</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45933</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45842</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45751</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44743</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1422000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1396000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1404000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1371000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1332000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1345000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1314000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1288000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1246000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1288000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1255000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1253000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1225000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1248000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1219000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1231000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>568000</v>
+        <v>572000</v>
       </c>
       <c r="E9" s="3">
         <v>568000</v>
       </c>
       <c r="F9" s="3">
+        <v>568000</v>
+      </c>
+      <c r="G9" s="3">
         <v>560000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>549000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>527000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>544000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>531000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>514000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>499000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>542000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>532000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>529000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>517000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>537000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>525000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>524000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>902000</v>
+      </c>
+      <c r="E10" s="3">
         <v>854000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>828000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>844000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>822000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>805000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>801000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>783000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>774000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>747000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>746000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>723000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>724000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>708000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>711000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>694000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>707000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,67 +957,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>68000</v>
+        <v>73000</v>
       </c>
       <c r="E12" s="3">
         <v>68000</v>
       </c>
       <c r="F12" s="3">
-        <v>67000</v>
+        <v>68000</v>
       </c>
       <c r="G12" s="3">
         <v>67000</v>
       </c>
       <c r="H12" s="3">
+        <v>67000</v>
+      </c>
+      <c r="I12" s="3">
         <v>64000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>69000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>63000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>61000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>60000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>57000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>55000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>57000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>56000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>53000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>52000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>55000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,55 +1079,58 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-7000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>15000</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>15000</v>
       </c>
       <c r="N14" s="3">
+        <v>15000</v>
+      </c>
+      <c r="O14" s="3">
         <v>6000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>21000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1122,52 +1141,55 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E15" s="3">
         <v>24000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>20000</v>
       </c>
       <c r="F15" s="3">
         <v>20000</v>
       </c>
       <c r="G15" s="3">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="H15" s="3">
         <v>19000</v>
       </c>
       <c r="I15" s="3">
+        <v>19000</v>
+      </c>
+      <c r="J15" s="3">
         <v>20000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>22000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>22000</v>
       </c>
       <c r="P15" s="3">
         <v>22000</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1181,8 +1203,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,126 +1226,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1159000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1084000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1079000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1078000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1058000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1010000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1037000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1006000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>989000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>953000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1001000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>976000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>958000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>933000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>954000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>934000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>929000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>315000</v>
+      </c>
+      <c r="E18" s="3">
         <v>338000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>317000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>326000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>313000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>322000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>308000</v>
       </c>
       <c r="J18" s="3">
         <v>308000</v>
       </c>
       <c r="K18" s="3">
+        <v>308000</v>
+      </c>
+      <c r="L18" s="3">
         <v>299000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>293000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>287000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>279000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>295000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>292000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>294000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>285000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>302000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,165 +1374,172 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-1000</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-14000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E21" s="3">
         <v>362000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>337000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>347000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>332000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>341000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>328000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>330000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>320000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>314000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>323000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>300000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>318000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>314000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>316000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>306000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>325000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E22" s="3">
         <v>24000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>27000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>30000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1519,126 +1558,135 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>289000</v>
+      </c>
+      <c r="E23" s="3">
         <v>321000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>293000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>306000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>285000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>289000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>280000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>286000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>270000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>250000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>261000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>268000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>275000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>292000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>295000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>285000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>302000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E24" s="3">
         <v>67000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>67000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>63000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>64000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>53000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>67000</v>
       </c>
       <c r="K24" s="3">
         <v>67000</v>
       </c>
       <c r="L24" s="3">
+        <v>67000</v>
+      </c>
+      <c r="M24" s="3">
         <v>66000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>61000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>63000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>66000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>67000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>79000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>67000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>71000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1744,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>254000</v>
+        <v>241000</v>
       </c>
       <c r="E26" s="3">
         <v>254000</v>
       </c>
       <c r="F26" s="3">
+        <v>254000</v>
+      </c>
+      <c r="G26" s="3">
         <v>239000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>222000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>225000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>227000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>219000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>203000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>184000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>200000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>205000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>209000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>225000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>216000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>218000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>231000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>254000</v>
+        <v>241000</v>
       </c>
       <c r="E27" s="3">
         <v>254000</v>
       </c>
       <c r="F27" s="3">
+        <v>254000</v>
+      </c>
+      <c r="G27" s="3">
         <v>239000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>222000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>225000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>227000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>219000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>203000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>184000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>205000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>209000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>225000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>216000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>218000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>231000</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1930,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1992,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2054,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,126 +2116,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>1000</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>14000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>254000</v>
+        <v>241000</v>
       </c>
       <c r="E33" s="3">
         <v>254000</v>
       </c>
       <c r="F33" s="3">
+        <v>254000</v>
+      </c>
+      <c r="G33" s="3">
         <v>239000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>222000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>225000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>227000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>219000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>203000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>184000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>200000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>205000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>209000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>225000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>216000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>218000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>231000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2302,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>254000</v>
+        <v>241000</v>
       </c>
       <c r="E35" s="3">
         <v>254000</v>
       </c>
       <c r="F35" s="3">
+        <v>254000</v>
+      </c>
+      <c r="G35" s="3">
         <v>239000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>222000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>225000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>227000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>219000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>203000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>184000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>200000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>205000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>209000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>225000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>216000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>218000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>231000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
         <v>46115</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45933</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45842</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45751</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44743</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2457,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,47 +2481,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2119000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1431000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2031000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1775000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1559000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1239000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1101000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1267000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1043000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>827000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>762000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>426000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,8 +2541,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2514,53 +2603,56 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>921000</v>
+      </c>
+      <c r="E43" s="3">
         <v>922000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>897000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>875000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>878000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>832000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>812000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>839000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>803000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>815000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>826000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>816000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>809000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>819000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,53 +2665,56 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>336000</v>
+      </c>
+      <c r="E44" s="3">
         <v>332000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>307000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>340000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>329000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>310000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>288000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>326000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>312000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>308000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>297000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>316000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>333000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>349000</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2632,50 +2727,53 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E45" s="3">
         <v>111000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>56000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>67000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>57000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>76000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>83000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,53 +2789,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3652000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2944000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3432000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3195000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2953000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2558000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2387000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2617000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2333000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2117000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2073000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1660000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1243000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1292000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,8 +2851,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2794,8 +2898,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2809,53 +2913,56 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E48" s="3">
         <v>496000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>489000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>472000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>463000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>449000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>427000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>426000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>417000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>423000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>406000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>376000</v>
       </c>
       <c r="O48" s="3">
         <v>376000</v>
       </c>
       <c r="P48" s="3">
+        <v>376000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>363000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2868,53 +2975,56 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3995000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3792000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3362000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3353000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3374000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3269000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3228000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2940000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2891000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2912000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2960000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2913000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2961000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2959000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,8 +3037,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3099,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,53 +3161,56 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E52" s="3">
         <v>421000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>42000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>409000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>381000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>369000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>55000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>280000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>262000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>256000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>44000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>211000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>207000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>231000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,8 +3223,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,53 +3285,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8558000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7653000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7693000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7429000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7171000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6645000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6406000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6263000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5903000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5708000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5693000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5160000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4787000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4845000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3347,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3373,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,53 +3397,54 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E57" s="3">
         <v>426000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>416000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>411000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>407000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>395000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>424000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>397000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>402000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>431000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>354000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>392000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>410000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,8 +3457,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3336,23 +3469,23 @@
         <v>700000</v>
       </c>
       <c r="E58" s="3">
+        <v>700000</v>
+      </c>
+      <c r="F58" s="3">
         <v>748000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>700000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>39000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -3360,11 +3493,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>33000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -3386,44 +3519,47 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>621000</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>567000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>617000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,53 +3581,56 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2057000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1984000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2056000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2037000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1275000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1170000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1245000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1226000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1190000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1156000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1265000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1034000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1010000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1026000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,53 +3643,56 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2893000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2172000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2131000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2170000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2862000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2814000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2728000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2813000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2777000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2784000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2744000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2736000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>131000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>119000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3563,53 +3705,56 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E62" s="3">
         <v>491000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>380000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>374000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>373000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>352000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>371000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>264000</v>
       </c>
       <c r="K62" s="3">
         <v>264000</v>
       </c>
       <c r="L62" s="3">
-        <v>280000</v>
+        <v>264000</v>
       </c>
       <c r="M62" s="3">
         <v>280000</v>
       </c>
       <c r="N62" s="3">
+        <v>280000</v>
+      </c>
+      <c r="O62" s="3">
         <v>131000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>360000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>352000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3767,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3829,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3891,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,53 +3953,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5460000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4647000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4587000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4581000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4510000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4336000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4361000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4303000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4231000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4220000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4304000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4117000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1501000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1497000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4015,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4041,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4101,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4163,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4225,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,44 +4287,47 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2175000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1966000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1744000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1522000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1310000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1114000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>917000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>717000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>521000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>340000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>178000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4170,14 +4343,17 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4411,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4473,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,53 +4535,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3097000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3005000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3105000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2847000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2653000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2302000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2038000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1954000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1666000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1482000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1383000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1038000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3281000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3343000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4597,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +4659,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
         <v>46115</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45933</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45842</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45751</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44743</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>254000</v>
+        <v>241000</v>
       </c>
       <c r="E81" s="3">
         <v>254000</v>
       </c>
       <c r="F81" s="3">
+        <v>254000</v>
+      </c>
+      <c r="G81" s="3">
         <v>239000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>222000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>225000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>227000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>219000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>203000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>184000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>200000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>205000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>209000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>225000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>216000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>218000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>231000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,8 +4814,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4641,43 +4839,46 @@
         <v>10000</v>
       </c>
       <c r="J83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K83" s="3">
         <v>9000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>10000</v>
       </c>
       <c r="L83" s="3">
         <v>10000</v>
       </c>
       <c r="M83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N83" s="3">
         <v>9000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>10000</v>
       </c>
       <c r="O83" s="3">
         <v>10000</v>
       </c>
       <c r="P83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>11000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>21000</v>
       </c>
       <c r="R83" s="3">
         <v>21000</v>
       </c>
       <c r="S83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="T83" s="3">
         <v>23000</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4936,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4998,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5060,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5122,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,67 +5184,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E89" s="3">
         <v>182000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>311000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>270000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>339000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>157000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>285000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>224000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>251000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>115000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>263000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>243000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>301000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>156000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>337000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>257000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>220000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,8 +5272,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5062,58 +5282,61 @@
         <v>-12000</v>
       </c>
       <c r="E91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-20000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-22000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5394,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,67 +5456,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-206000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-439000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-394000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-43000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5544,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5321,31 +5554,31 @@
         <v>32000</v>
       </c>
       <c r="E96" s="3">
+        <v>32000</v>
+      </c>
+      <c r="F96" s="3">
         <v>27000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>28000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>27000</v>
       </c>
       <c r="H96" s="3">
         <v>27000</v>
       </c>
       <c r="I96" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J96" s="3">
         <v>22000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>23000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>22000</v>
       </c>
       <c r="L96" s="3">
         <v>22000</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>3</v>
+      <c r="M96" s="3">
+        <v>22000</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>3</v>
@@ -5356,8 +5589,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5371,8 +5604,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5666,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5728,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,94 +5790,100 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>558000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-332000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-25000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-36000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-15000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-16000</v>
       </c>
       <c r="J100" s="3">
         <v>-16000</v>
       </c>
       <c r="K100" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="L100" s="3">
         <v>-13000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>97000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>206000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-291000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-147000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-325000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-214000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-209000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E101" s="3">
         <v>18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-41000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>22000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-11000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5660,53 +5908,56 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>688000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>256000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>216000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>320000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>138000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-166000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>224000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>216000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>65000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>336000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>426000</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
@@ -5719,10 +5970,13 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
